--- a/artfynd/A 17508-2026 artfynd.xlsx
+++ b/artfynd/A 17508-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112967273</v>
+        <v>129069776</v>
       </c>
       <c r="B2" t="n">
-        <v>56781</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4374</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövlund, 250 m NV, Srm</t>
+          <t>Strömslund, Strömslund, ekhage 400 m NO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591287</v>
+        <v>591110</v>
       </c>
       <c r="R2" t="n">
-        <v>6538611</v>
+        <v>6538514</v>
       </c>
       <c r="S2" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130323932</v>
+        <v>112967273</v>
       </c>
       <c r="B3" t="n">
-        <v>57858</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -876,22 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,6 +909,330 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130323932</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lövlund, 250 m NV, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591287</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6538611</v>
+      </c>
+      <c r="S4" t="n">
+        <v>46</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Flodin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133813091</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Annebäck V om , Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591127</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6538584</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133812923</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103908</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>225103</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig sälg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Annebäck V om , Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>591252</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6538598</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vadsbro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17508-2026 artfynd.xlsx
+++ b/artfynd/A 17508-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129069776</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112967273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130323932</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133813091</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,8 +1258,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133812923</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>